--- a/data_extactor/batch/401_450.xlsx
+++ b/data_extactor/batch/401_450.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sarbazi\code\sarbazi\data_extactor\batch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC573A9-6788-4E44-9B05-92DE78AE5619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9824AB30-CB9A-4FB1-AA72-06C27A777F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="545">
   <si>
     <t>27-3043.05</t>
   </si>
@@ -1546,6 +1546,120 @@
   </si>
   <si>
     <t>Advise patients and community members concerning diet, activity, hygiene, and disease prevention. | Collect, record, and maintain patient information, such as medical history, reports, or examination results. | Coordinate work with nurses, social workers, rehabilitation therapists, pharmacists, psychologists, and other health care providers. | Direct and coordinate activities of nurses, students, assistants, specialists, therapists, and other medical staff. | Explain procedures and discuss test results or prescribed treatments with patients. | Monitor patients' conditions and progress and reevaluate treatments as necessary. | Order, perform, and interpret tests and analyze records, reports, and examination information to diagnose patients' condition. | Plan, implement, or administer health programs or standards in hospitals, businesses, or communities for prevention or treatment of injury or illness. | Prepare government or organizational reports which include birth, death, and disease statistics, workforce evaluations, or medical status of individuals. | Prescribe or administer treatment, therapy, medication, vaccination, and other specialized medical care to treat or prevent illness, disease, or injury. | Refer patients to medical specialists or other practitioners when necessary. | Train residents, medical students, and other health care professionals.</t>
+  </si>
+  <si>
+    <t>Communications Assistant | Communications Specialist | Content Creator | Copywriter | Media Coordinator | Media Specialist | Proofreader | Publications Specialist | Script Reader | Social Media Specialist</t>
+  </si>
+  <si>
+    <t>Adobe Photoshop | Adobe Illustrator | Adobe InDesign | Adobe Acrobat | Graphics software | Microsoft Word | Microsoft Excel | Email software | Web browser software | Microsoft PowerPoint | Graphics editing software | Microsoft Office software | Microsoft Outlook | Microsoft Access | Microsoft SharePoint | Database software | Google Docs | Calendar management software | Spreadsheet programs</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Active Listening | Speaking | Writing | Monitoring | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Communications and Media | English Language | Computers and Electronics | Sales and Marketing | Customer and Personal Service | Fine Arts | Administration and Management | Education and Training</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Level of Competition</t>
+  </si>
+  <si>
+    <t>Editors | Technical Writers | Writers and Authors | Poets, Lyricists and Creative Writers | Public Relations Specialists | News Analysts, Reporters, and Journalists | Interpreters and Translators | Court Reporters and Simultaneous Captioners | Broadcast Announcers and Radio Disc Jockeys | Graphic Designers | Art Directors | Producers and Directors | Media Programming Directors | Market Research Analysts and Marketing Specialists | Public Relations Managers | Marketing Managers | Web and Digital Interface Designers | Photographers | Film and Video Editors | Communications Teachers, Postsecondary</t>
+  </si>
+  <si>
+    <t>Perform media and communication work in specialties not classified separately. | Write, edit, and proofread content for print, broadcast, and digital channels. | Develop communication plans, messaging, and editorial calendars. | Research topics and verify facts, sources, and permissions. | Coordinate production schedules with writers, designers, and vendors. | Adapt content for different audiences, formats, and platforms. | Manage social media accounts and monitor audience engagement. | Review submissions and recommend material for publication or production. | Maintain style guides, content libraries, and asset archives. | Track performance metrics and prepare reports on content reach and impact. | Obtain approvals and ensure compliance with legal and brand requirements. | Assist with event promotion, press materials, and media relations. | Coordinate translation, captioning, and accessibility of published materials. | Support budgeting and vendor management for communication projects.</t>
+  </si>
+  <si>
+    <t>Followspot Operator | Gaffer | Light Board Operator | Lighting Designer | Lighting Director | Lighting Operator | Lighting Technician | Stage Electrician | Studio Lighting Technician | Electrician, Stage</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Monitoring | Active Listening | Speaking | Mathematics | Active Learning</t>
+  </si>
+  <si>
+    <t>Computers and Electronics | Fine Arts | Engineering and Technology | English Language | Communications and Media | Design | Public Safety and Security | Mechanical</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Near Vision | Visualization | Arm-Hand Steadiness | Finger Dexterity | Manual Dexterity | Control Precision | Multilimb Coordination | Selective Attention | Category Flexibility | Mathematical Reasoning | Far Vision | Visual Color Discrimination | Reaction Time</t>
+  </si>
+  <si>
+    <t>Face-to-Face Discussions with Individuals and Within Teams | Work With or Contribute to a Work Group or Team | Contact With Others | Spend Time Standing | Indoors, Not Environmentally Controlled | Spend Time Climbing Ladders, Scaffolds, or Poles | Exposed to High Places | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Exposed to Hazardous Equipment | Health and Safety of Other Workers | Time Pressure | Consequence of Error | Importance of Being Exact or Accurate | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Very Hot or Cold Temperatures | Physical Proximity | Freedom to Make Decisions | E-Mail | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable</t>
+  </si>
+  <si>
+    <t>Audiovisual Technician | AV Support Specialist | Broadcast Equipment Technician | Media Equipment Operator | Multimedia Technician | Production Assistant | Projectionist | Stage Technician | Studio Technician | Video Technician</t>
+  </si>
+  <si>
+    <t>Adobe Photoshop | Adobe Illustrator | Adobe InDesign | Adobe Acrobat | Graphics software | Microsoft Word | Microsoft Excel | Email software | Web browser software | Microsoft PowerPoint | Graphics editing software | Microsoft Office software | Microsoft Windows | Computerized maintenance management system CMMS</t>
+  </si>
+  <si>
+    <t>Telecommunications | Computers and Electronics | Communications and Media | English Language | Engineering and Technology | Fine Arts | Customer and Personal Service</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Near Vision | Visualization | Arm-Hand Steadiness | Finger Dexterity | Manual Dexterity | Control Precision | Multilimb Coordination | Selective Attention | Category Flexibility | Mathematical Reasoning | Far Vision</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Indoors, Not Environmentally Controlled | Time Pressure | Importance of Being Exact or Accurate | Consequence of Error | Exposed to Sounds, Noise Levels that are Distracting or Uncomfortable | Spend Time Climbing Ladders, Scaffolds, or Poles | Exposed to Hazardous Equipment</t>
+  </si>
+  <si>
+    <t>Audio and Video Technicians | Broadcast Technicians | Sound Engineering Technicians | Lighting Technicians | Camera Operators, Television, Video, and Film | Film and Video Editors | Photographers | Media Technical Directors/Managers | Producers and Directors | Telecommunications Equipment Installers and Repairers, Except Line Installers | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Radio, Cellular, and Tower Equipment Installers and Repairers | Computer User Support Specialists | Special Effects Artists and Animators | Set and Exhibit Designers | Media Programming Directors | Audiovisual Equipment Installers and Repairers | Electricians | Stationary Engineers and Boiler Operators | Media and Communication Workers, All Other</t>
+  </si>
+  <si>
+    <t>Operate and maintain media and communication equipment in roles not classified separately. | Set up, connect, test, and operate audio, video, lighting, and projection equipment. | Monitor signal quality and adjust equipment to maintain broadcast or presentation standards. | Diagnose equipment malfunctions and perform repairs or arrange servicing. | Install and configure cabling, mounts, and control systems. | Record, duplicate, and archive audio and video material. | Coordinate technical requirements with producers, presenters, and event staff. | Operate equipment during live events, broadcasts, and recordings. | Maintain inventories of equipment, media, spare parts, and consumables. | Perform preventive maintenance and keep service records. | Strike and store equipment safely after events and productions. | Train users on operation of presentation and recording equipment. | Follow electrical and rigging safety procedures during setup and operation. | Recommend equipment purchases and upgrades based on technical requirements.</t>
+  </si>
+  <si>
+    <t>Dental Anesthesiologist | Dental Public Health Specialist | Endodontist | Oral Pathologist | Oral Radiologist | Pediatric Dentist | Periodontist | Dental Specialist | Oral Medicine Specialist | Orofacial Pain Specialist</t>
+  </si>
+  <si>
+    <t>Electronic medical record EMR software | Medical procedure coding software | Microsoft Excel | Microsoft Word | Email software | Database software | Scheduling software | Microsoft Outlook | Web browser software | Microsoft Office software | Microsoft PowerPoint</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Active Listening | Critical Thinking | Speaking | Science | Monitoring | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Medicine and Dentistry | Biology | Chemistry | Customer and Personal Service | English Language | Psychology | Administration and Management | Education and Training | Therapy and Counseling</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Near Vision | Speech Clarity | Speech Recognition | Finger Dexterity | Arm-Hand Steadiness | Manual Dexterity | Selective Attention | Category Flexibility | Visualization | Time Sharing | Control Precision | Depth Perception | Visual Color Discrimination</t>
+  </si>
+  <si>
+    <t>Exposed to Disease or Infections | Physical Proximity | Contact With Others | Deal With External Customers or the Public in General | Consequence of Error | Importance of Being Exact or Accurate | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Frequency of Decision Making | Health and Safety of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | E-Mail | Work With or Contribute to a Work Group or Team | Time Pressure | Indoors, Environmentally Controlled | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Coordinate or Lead Others in Accomplishing Work Activities | Impact of Decisions on Co-workers or Company Results</t>
+  </si>
+  <si>
+    <t>Dentists, General | Orthodontists | Prosthodontists | Oral and Maxillofacial Surgeons | Dental Hygienists | Dental Assistants | Physicians, All Other | Surgeons, All Other | Anesthesiologists | Physicians, Pathologists | Family Medicine Physicians | Pediatricians, General | Health Specialties Teachers, Postsecondary | Medical and Health Services Managers | Orthotists and Prosthetists | Surgical Assistants | Radiologic Technologists and Technicians | Healthcare Diagnosing or Treating Practitioners, All Other | Acupuncturists | Naturopathic Physicians</t>
+  </si>
+  <si>
+    <t>Diagnose and treat conditions of the teeth, gums, and oral cavity in specialties not listed separately. | Examine patients and review medical and dental histories to determine treatment needs. | Order, perform, and interpret diagnostic images and laboratory tests. | Develop and explain treatment plans, risks, alternatives, and costs to patients. | Administer local, sedative, or general anesthesia as indicated by the procedure. | Perform specialized surgical and restorative procedures within the area of practice. | Prescribe medications, including antibiotics and analgesics, and monitor responses. | Manage complications, emergencies, and post-operative care. | Refer patients to other specialists and coordinate multidisciplinary treatment. | Maintain complete and accurate patient records and treatment documentation. | Supervise dental hygienists, assistants, and laboratory technicians. | Enforce infection control, radiation safety, and sterilization protocols. | Educate patients on oral hygiene, prevention, and post-treatment care. | Maintain licensure and clinical competence through continuing education. | Manage practice operations, including scheduling, billing, and supply procurement.</t>
+  </si>
+  <si>
+    <t>Behavioral Therapist | Dance Therapist | Drama Therapist | Horticultural Therapist | Hypnotherapist | Kinesiotherapist | Rehabilitation Therapist | Therapist | Vocational Rehabilitation Therapist | Play Therapist</t>
+  </si>
+  <si>
+    <t>Electronic medical record EMR software | Medical procedure coding software | Microsoft Excel | Microsoft Word | Email software | Database software | Scheduling software | Microsoft Outlook | Web browser software | Microsoft Office software</t>
+  </si>
+  <si>
+    <t>Therapy and Counseling | Psychology | Medicine and Dentistry | Customer and Personal Service | English Language | Education and Training | Biology | Sociology and Anthropology</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Near Vision | Speech Clarity | Speech Recognition | Finger Dexterity | Arm-Hand Steadiness | Manual Dexterity | Selective Attention | Category Flexibility | Visualization | Time Sharing</t>
+  </si>
+  <si>
+    <t>Occupational Therapists | Physical Therapists | Recreational Therapists | Respiratory Therapists | Radiation Therapists | Speech-Language Pathologists | Art Therapists | Music Therapists | Exercise Physiologists | Low Vision Therapists, Orientation and Mobility Specialists, and Vision Rehabilitation Therapists | Marriage and Family Therapists | Mental Health Counselors | Rehabilitation Counselors | Clinical and Counseling Psychologists | Athletic Trainers | Occupational Therapy Assistants | Physical Therapist Assistants | Healthcare Social Workers | Health Education Specialists | Healthcare Diagnosing or Treating Practitioners, All Other</t>
+  </si>
+  <si>
+    <t>Provide therapy services in specialties not classified separately. | Evaluate patients to determine functional limitations, needs, and therapeutic goals. | Develop individualized treatment plans and select appropriate therapeutic modalities. | Administer therapy sessions and adjust interventions based on patient response. | Instruct patients and caregivers in exercises, techniques, and home programs. | Document evaluations, treatments, and progress in patient records. | Confer with physicians and other providers about patient care plans. | Measure and record patient progress against established objectives. | Recommend adaptive equipment, assistive devices, and environmental modifications. | Educate patients and families about conditions, prognosis, and self-management. | Ensure compliance with clinical protocols, safety standards, and privacy rules. | Coordinate discharge planning and referrals to community resources. | Supervise therapy assistants, aides, and students. | Maintain licensure and clinical skills through continuing education.</t>
+  </si>
+  <si>
+    <t>Cardiac Electrophysiologist | Cardiologist | Cardiovascular Disease Specialist | Cardiovascular Physician | Echocardiographer | Heart Specialist | Interventional Cardiologist | Noninvasive Cardiologist | Pediatric Cardiologist | Preventive Cardiologist</t>
+  </si>
+  <si>
+    <t>Medicine and Dentistry | Biology | Chemistry | Customer and Personal Service | English Language | Psychology | Education and Training | Physics | Administration and Management | Therapy and Counseling</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Near Vision | Speech Clarity | Speech Recognition | Finger Dexterity | Arm-Hand Steadiness | Manual Dexterity | Selective Attention | Category Flexibility | Visualization | Time Sharing | Control Precision | Depth Perception</t>
+  </si>
+  <si>
+    <t>Exposed to Disease or Infections | Physical Proximity | Contact With Others | Deal With External Customers or the Public in General | Consequence of Error | Importance of Being Exact or Accurate | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Spend Time Standing | Frequency of Decision Making | Health and Safety of Other Workers | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | E-Mail | Work With or Contribute to a Work Group or Team | Time Pressure | Indoors, Environmentally Controlled | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Coordinate or Lead Others in Accomplishing Work Activities | Exposed to Radiation | Impact of Decisions on Co-workers or Company Results</t>
   </si>
 </sst>
 </file>
@@ -1978,8 +2092,32 @@
       <c r="B4" t="s">
         <v>34</v>
       </c>
+      <c r="C4" t="s">
+        <v>507</v>
+      </c>
+      <c r="D4" t="s">
+        <v>508</v>
+      </c>
+      <c r="E4" t="s">
+        <v>509</v>
+      </c>
+      <c r="F4" t="s">
+        <v>510</v>
+      </c>
+      <c r="G4" t="s">
+        <v>511</v>
+      </c>
+      <c r="H4" t="s">
+        <v>512</v>
+      </c>
+      <c r="I4" t="s">
+        <v>513</v>
+      </c>
       <c r="J4" t="s">
         <v>35</v>
+      </c>
+      <c r="K4" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -2094,8 +2232,23 @@
       <c r="B8" t="s">
         <v>70</v>
       </c>
+      <c r="C8" t="s">
+        <v>515</v>
+      </c>
       <c r="D8" t="s">
         <v>71</v>
+      </c>
+      <c r="E8" t="s">
+        <v>516</v>
+      </c>
+      <c r="F8" t="s">
+        <v>517</v>
+      </c>
+      <c r="G8" t="s">
+        <v>518</v>
+      </c>
+      <c r="H8" t="s">
+        <v>519</v>
       </c>
       <c r="I8" t="s">
         <v>72</v>
@@ -2219,8 +2372,32 @@
       <c r="B12" t="s">
         <v>109</v>
       </c>
+      <c r="C12" t="s">
+        <v>520</v>
+      </c>
+      <c r="D12" t="s">
+        <v>521</v>
+      </c>
+      <c r="E12" t="s">
+        <v>516</v>
+      </c>
+      <c r="F12" t="s">
+        <v>522</v>
+      </c>
+      <c r="G12" t="s">
+        <v>523</v>
+      </c>
+      <c r="H12" t="s">
+        <v>524</v>
+      </c>
+      <c r="I12" t="s">
+        <v>525</v>
+      </c>
       <c r="J12" t="s">
         <v>110</v>
+      </c>
+      <c r="K12" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -2405,8 +2582,32 @@
       <c r="B18" t="s">
         <v>167</v>
       </c>
+      <c r="C18" t="s">
+        <v>527</v>
+      </c>
+      <c r="D18" t="s">
+        <v>528</v>
+      </c>
+      <c r="E18" t="s">
+        <v>529</v>
+      </c>
+      <c r="F18" t="s">
+        <v>530</v>
+      </c>
+      <c r="G18" t="s">
+        <v>531</v>
+      </c>
+      <c r="H18" t="s">
+        <v>532</v>
+      </c>
+      <c r="I18" t="s">
+        <v>533</v>
+      </c>
       <c r="J18" t="s">
         <v>168</v>
+      </c>
+      <c r="K18" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
@@ -2906,8 +3107,32 @@
       <c r="B33" t="s">
         <v>324</v>
       </c>
+      <c r="C33" t="s">
+        <v>535</v>
+      </c>
+      <c r="D33" t="s">
+        <v>536</v>
+      </c>
+      <c r="E33" t="s">
+        <v>529</v>
+      </c>
+      <c r="F33" t="s">
+        <v>537</v>
+      </c>
+      <c r="G33" t="s">
+        <v>538</v>
+      </c>
+      <c r="H33" t="s">
+        <v>532</v>
+      </c>
+      <c r="I33" t="s">
+        <v>539</v>
+      </c>
       <c r="J33" t="s">
         <v>325</v>
+      </c>
+      <c r="K33" t="s">
+        <v>540</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
@@ -3372,8 +3597,23 @@
       <c r="B47" t="s">
         <v>469</v>
       </c>
+      <c r="C47" t="s">
+        <v>541</v>
+      </c>
       <c r="D47" t="s">
         <v>470</v>
+      </c>
+      <c r="E47" t="s">
+        <v>529</v>
+      </c>
+      <c r="F47" t="s">
+        <v>542</v>
+      </c>
+      <c r="G47" t="s">
+        <v>543</v>
+      </c>
+      <c r="H47" t="s">
+        <v>544</v>
       </c>
       <c r="I47" t="s">
         <v>471</v>
